--- a/fixtures/messy-06-variants-in-row.xlsx
+++ b/fixtures/messy-06-variants-in-row.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Item</t>
   </si>
@@ -74,6 +74,30 @@
   </si>
   <si>
     <t>White</t>
+  </si>
+  <si>
+    <t>Ghee Tin</t>
+  </si>
+  <si>
+    <t>1/2 kg</t>
+  </si>
+  <si>
+    <t>Plain</t>
+  </si>
+  <si>
+    <t>Rice Bag</t>
+  </si>
+  <si>
+    <t>5 kg / 10 kg</t>
+  </si>
+  <si>
+    <t>Sona Masoori</t>
+  </si>
+  <si>
+    <t>Sleeve Style Shirt</t>
+  </si>
+  <si>
+    <t>Half Sleeve / Full Sleeve</t>
   </si>
 </sst>
 </file>
@@ -450,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -552,6 +576,57 @@
         <v>8</v>
       </c>
     </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7">
+        <v>450</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>320</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>890</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
